--- a/python/output/network_report.xlsx
+++ b/python/output/network_report.xlsx
@@ -1249,7 +1249,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1d00h</t>
+          <t>1d06h</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1d00h</t>
+          <t>1d06h</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1d00h</t>
+          <t>1d06h</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1d00h</t>
+          <t>1d06h</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>

--- a/python/output/network_report.xlsx
+++ b/python/output/network_report.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ip_int_brief" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cdp_neighbors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ip_route" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ip_interface_bri" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ip_ospf_neighbor" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,27 +736,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>neighbor_name</t>
+          <t>neighbor_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>local_interface</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>capabilities</t>
+          <t>state</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>dead_time</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>neighbor_interface</t>
+          <t>ip_address</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>interface</t>
         </is>
       </c>
     </row>
@@ -769,27 +773,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Router-02.lab.local</t>
+          <t>10.0.0.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eth 0/0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>FULL/DROTHER</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>00:00:31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Uni Eth 0/0</t>
+          <t>10.0.0.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ethernet0/1</t>
         </is>
       </c>
     </row>
@@ -801,856 +810,108 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Router-02.lab.local</t>
+          <t>10.255.0.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eth 0/1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>FULL/DR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>00:00:33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uni Eth 0/1</t>
+          <t>10.0.0.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ethernet0/1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Router-01</t>
+          <t>Router-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Router-03.lab.local</t>
+          <t>10.0.0.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eth 0/1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>FULL/DROTHER</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>00:00:38</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uni Eth 0/1</t>
+          <t>10.0.0.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ethernet0/1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Router-01</t>
+          <t>Router-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Router-03.lab.local</t>
+          <t>10.255.0.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eth 0/0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>FULL/BDR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>00:00:32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uni Eth 0/0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Router-01.lab.local</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Eth 0/1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Linux</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Uni Eth 0/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Router-01.lab.local</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Eth 0/0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Linux</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Uni Eth 0/0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Router-03.lab.local</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Eth 0/1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Linux</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Uni Eth 0/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Router-03.lab.local</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Eth 0/0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Linux</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Uni Eth 0/0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>hostname</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>vrf</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>protocol</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>prefix_length</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>nexthop_ip</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>nexthop_vrf</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>nexthop_if</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>uptime</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>flag</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10.0.0.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+          <t>10.0.0.1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Ethernet0/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10.0.0.1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>10.255.0.1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10.255.0.2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10.0.0.2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1d06h</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10.255.0.3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10.0.0.3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1d06h</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>192.168.1.0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Ethernet0/0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>192.168.1.11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Ethernet0/0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10.0.0.0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>10.0.0.2</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10.255.0.1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10.0.0.1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1d06h</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>10.255.0.2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>10.255.0.3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10.0.0.3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1d06h</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>192.168.1.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Ethernet0/0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>192.168.1.12</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Ethernet0/0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/python/output/network_report.xlsx
+++ b/python/output/network_report.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ip_interface_bri" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ip_ospf_neighbor" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,203 +716,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>hostname</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>neighbor_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>dead_time</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ip_address</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>interface</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10.0.0.3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FULL/DROTHER</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>00:00:31</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10.0.0.3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Router-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10.255.0.2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FULL/DR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>00:00:33</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10.0.0.2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10.0.0.3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FULL/DROTHER</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>00:00:38</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10.0.0.3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Router-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>10.255.0.1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FULL/BDR</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00:00:32</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10.0.0.1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Ethernet0/1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>